--- a/EXCEL UTILITARIOS/Calculadora de Recargos Ajustada - V2_ Segun Frecuencia_2105 DZalles.xlsx
+++ b/EXCEL UTILITARIOS/Calculadora de Recargos Ajustada - V2_ Segun Frecuencia_2105 DZalles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\DATOS TRABAJO\NUEVO CORE\ORACLE_SQL\EXCEL UTILITARIOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA32EAA2-76E2-4456-A7CD-8EA3FA82BE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E9077D-5042-4FE3-8649-61AAA898F8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="751" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="751" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FRECUENCIAS" sheetId="18" r:id="rId1"/>
@@ -2764,7 +2764,7 @@
         <v>42</v>
       </c>
       <c r="F2" s="115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" s="116"/>
       <c r="H2" s="117"/>
@@ -2828,7 +2828,8 @@
       </c>
       <c r="E4" s="108"/>
       <c r="F4" s="98">
-        <v>2049.8222000000001</v>
+        <f>2819.87+2387.808</f>
+        <v>5207.6779999999999</v>
       </c>
       <c r="G4" s="99">
         <v>0</v>
@@ -2838,11 +2839,11 @@
       </c>
       <c r="I4" s="94">
         <f>IF(B4="SI",IF($D4="SI",($F4+$G4+$H4) / (1- SUM($D$16:$D$20)),$F4),0)</f>
-        <v>2627.9771794871795</v>
+        <v>6676.5102564102563</v>
       </c>
       <c r="J4" s="148">
         <f>$K$3*$I4</f>
-        <v>230.5235302074359</v>
+        <v>585.65680318205125</v>
       </c>
       <c r="L4" s="10"/>
     </row>
@@ -2858,17 +2859,17 @@
       </c>
       <c r="E5" s="92"/>
       <c r="F5" s="100">
-        <v>0</v>
+        <v>1185.5332000000001</v>
       </c>
       <c r="G5" s="101"/>
       <c r="H5" s="144"/>
       <c r="I5" s="123">
         <f>IF(B5="SI",IF($D5="SI",($F5+$G5+$H5) / (1- SUM($D$16:$D$20)),$F5),0)</f>
-        <v>0</v>
+        <v>1519.9143589743589</v>
       </c>
       <c r="J5" s="149">
         <f t="shared" ref="J5:J14" si="0">$K$3*$I5</f>
-        <v>0</v>
+        <v>133.3253676548718</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -2886,17 +2887,17 @@
       </c>
       <c r="F6" s="102">
         <f>E6*$F$2</f>
-        <v>21.84</v>
+        <v>43.68</v>
       </c>
       <c r="G6" s="101"/>
       <c r="H6" s="144"/>
       <c r="I6" s="123">
         <f t="shared" ref="I6:I14" si="1">IF(B6="SI",IF($D6="SI",($F6+$G6+$H6) / (1- SUM($D$16:$D$20)),$F6),0)</f>
-        <v>21.84</v>
+        <v>43.68</v>
       </c>
       <c r="J6" s="149">
         <f t="shared" si="0"/>
-        <v>1.91578296</v>
+        <v>3.8315659200000001</v>
       </c>
     </row>
     <row r="7" spans="2:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -2970,17 +2971,17 @@
       </c>
       <c r="F9" s="102">
         <f t="shared" si="2"/>
-        <v>54.6</v>
+        <v>109.2</v>
       </c>
       <c r="G9" s="103"/>
       <c r="H9" s="145"/>
       <c r="I9" s="123">
         <f t="shared" si="1"/>
-        <v>54.6</v>
+        <v>109.2</v>
       </c>
       <c r="J9" s="149">
         <f t="shared" si="0"/>
-        <v>4.7894574000000008</v>
+        <v>9.5789148000000015</v>
       </c>
     </row>
     <row r="10" spans="2:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -2998,17 +2999,17 @@
       </c>
       <c r="F10" s="102">
         <f t="shared" si="2"/>
-        <v>80.64</v>
+        <v>161.28</v>
       </c>
       <c r="G10" s="103"/>
       <c r="H10" s="145"/>
       <c r="I10" s="123">
         <f t="shared" si="1"/>
-        <v>80.64</v>
+        <v>161.28</v>
       </c>
       <c r="J10" s="149">
         <f t="shared" si="0"/>
-        <v>7.0736601600000002</v>
+        <v>14.14732032</v>
       </c>
     </row>
     <row r="11" spans="2:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -3026,17 +3027,17 @@
       </c>
       <c r="F11" s="102">
         <f t="shared" si="2"/>
-        <v>44.377200000000002</v>
+        <v>88.754400000000004</v>
       </c>
       <c r="G11" s="103"/>
       <c r="H11" s="145"/>
       <c r="I11" s="123">
         <f t="shared" si="1"/>
-        <v>44.377200000000002</v>
+        <v>88.754400000000004</v>
       </c>
       <c r="J11" s="149">
         <f t="shared" si="0"/>
-        <v>3.8927236068000006</v>
+        <v>7.7854472136000012</v>
       </c>
     </row>
     <row r="12" spans="2:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -3112,17 +3113,17 @@
       <c r="E15" s="140"/>
       <c r="F15" s="141">
         <f>SUM(F4:F14)</f>
-        <v>2251.2793999999999</v>
+        <v>6796.1255999999994</v>
       </c>
       <c r="G15" s="142"/>
       <c r="H15" s="138"/>
       <c r="I15" s="151">
         <f>SUM(I4:I14)</f>
-        <v>2829.4343794871793</v>
+        <v>8599.3390153846158</v>
       </c>
       <c r="J15" s="124">
         <f>SUM(J4:J14)</f>
-        <v>248.19515433423589</v>
+        <v>754.32541909052304</v>
       </c>
     </row>
     <row r="16" spans="2:14" ht="18" x14ac:dyDescent="0.35">
@@ -3141,11 +3142,11 @@
       <c r="H16" s="93"/>
       <c r="I16" s="120">
         <f>$I$4*$D16</f>
-        <v>394.19657692307692</v>
+        <v>1001.4765384615384</v>
       </c>
       <c r="J16" s="22">
         <f>$J$4*$D16</f>
-        <v>34.578529531115386</v>
+        <v>87.848520477307687</v>
       </c>
     </row>
     <row r="17" spans="2:10" ht="18" x14ac:dyDescent="0.35">
@@ -3162,11 +3163,11 @@
       <c r="H17" s="26"/>
       <c r="I17" s="119">
         <f>$I$4*$D17</f>
-        <v>131.39885897435897</v>
+        <v>333.82551282051281</v>
       </c>
       <c r="J17" s="24">
         <f t="shared" ref="J17:J20" si="3">$J$4*$D17</f>
-        <v>11.526176510371796</v>
+        <v>29.282840159102562</v>
       </c>
     </row>
     <row r="18" spans="2:10" ht="18" x14ac:dyDescent="0.35">
@@ -3183,11 +3184,11 @@
       <c r="H18" s="26"/>
       <c r="I18" s="119">
         <f>$I$4*$D18</f>
-        <v>26.279771794871795</v>
+        <v>66.765102564102563</v>
       </c>
       <c r="J18" s="24">
         <f t="shared" si="3"/>
-        <v>2.305235302074359</v>
+        <v>5.8565680318205127</v>
       </c>
     </row>
     <row r="19" spans="2:10" ht="18" x14ac:dyDescent="0.35">
@@ -3204,11 +3205,11 @@
       <c r="H19" s="26"/>
       <c r="I19" s="119">
         <f>$I$4*$D19</f>
-        <v>26.279771794871795</v>
+        <v>66.765102564102563</v>
       </c>
       <c r="J19" s="24">
         <f t="shared" si="3"/>
-        <v>2.305235302074359</v>
+        <v>5.8565680318205127</v>
       </c>
     </row>
     <row r="20" spans="2:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
@@ -3242,11 +3243,11 @@
       <c r="H21" s="135"/>
       <c r="I21" s="136">
         <f>I15/(1-$D$22)</f>
-        <v>3536.7929743589739</v>
+        <v>10749.173769230769</v>
       </c>
       <c r="J21" s="125">
         <f>J15/(1-$D$22)</f>
-        <v>310.24394291779487</v>
+        <v>942.90677386315372</v>
       </c>
     </row>
     <row r="22" spans="2:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
@@ -3262,11 +3263,11 @@
       <c r="H22" s="20"/>
       <c r="I22" s="120">
         <f>$I$21*$D22</f>
-        <v>707.35859487179482</v>
+        <v>2149.8347538461539</v>
       </c>
       <c r="J22" s="127">
         <f>$J$21*$D22</f>
-        <v>62.048788583558974</v>
+        <v>188.58135477263076</v>
       </c>
     </row>
     <row r="23" spans="2:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
@@ -3284,7 +3285,7 @@
         <v>5</v>
       </c>
       <c r="D24" s="111">
-        <v>0.02</v>
+        <v>1.4800000000000001E-2</v>
       </c>
       <c r="E24" s="167"/>
       <c r="F24" s="8"/>
@@ -3292,11 +3293,11 @@
       <c r="H24" s="8"/>
       <c r="I24" s="122">
         <f>$I$28*$D24</f>
-        <v>88.419824358974353</v>
+        <v>214.78059479574753</v>
       </c>
       <c r="J24" s="22">
         <f>$J$28*$D24</f>
-        <v>7.7560985729448717</v>
+        <v>18.840338994888175</v>
       </c>
     </row>
     <row r="25" spans="2:10" ht="18" x14ac:dyDescent="0.35">
@@ -3304,7 +3305,7 @@
         <v>26</v>
       </c>
       <c r="D25" s="35">
-        <v>0.02</v>
+        <v>8.4501000000000007E-2</v>
       </c>
       <c r="E25" s="165"/>
       <c r="F25" s="9"/>
@@ -3312,11 +3313,11 @@
       <c r="H25" s="9"/>
       <c r="I25" s="119">
         <f>$I$28*$D25</f>
-        <v>88.419824358974353</v>
+        <v>1226.2956108672608</v>
       </c>
       <c r="J25" s="24">
         <f t="shared" ref="J25:J27" si="4">$J$28*$D25</f>
-        <v>7.7560985729448717</v>
+        <v>107.56942468966524</v>
       </c>
     </row>
     <row r="26" spans="2:10" ht="18" x14ac:dyDescent="0.35">
@@ -3332,11 +3333,11 @@
       <c r="H26" s="40"/>
       <c r="I26" s="119">
         <f>$I$28*$D26</f>
-        <v>132.62973653846151</v>
+        <v>435.36607053192063</v>
       </c>
       <c r="J26" s="24">
         <f t="shared" si="4"/>
-        <v>11.634147859417308</v>
+        <v>38.189876340989535</v>
       </c>
     </row>
     <row r="27" spans="2:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
@@ -3352,11 +3353,11 @@
       <c r="H27" s="25"/>
       <c r="I27" s="119">
         <f>$I$28*$D27</f>
-        <v>574.72885833333328</v>
+        <v>1886.5863056383228</v>
       </c>
       <c r="J27" s="24">
         <f t="shared" si="4"/>
-        <v>50.414640724141663</v>
+        <v>165.48946414428801</v>
       </c>
     </row>
     <row r="28" spans="2:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
@@ -3370,11 +3371,11 @@
       <c r="H28" s="176"/>
       <c r="I28" s="151">
         <f>I21/(1-SUM($D$24:$D$27))</f>
-        <v>4420.9912179487173</v>
+        <v>14512.202351064021</v>
       </c>
       <c r="J28" s="177">
         <f>J21/(1-SUM($D$24:$D$27))</f>
-        <v>387.80492864724357</v>
+        <v>1272.9958780329846</v>
       </c>
     </row>
   </sheetData>
